--- a/public/sandbox-dados.xlsx
+++ b/public/sandbox-dados.xlsx
@@ -1789,7 +1789,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2073,16 +2073,345 @@
         <v>2026-06-01T12:00:00.000Z</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>tom-6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Alfa Construções Ltda</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Alfa</v>
+      </c>
+      <c r="D7" t="str">
+        <v>06.006.006/0001-06</v>
+      </c>
+      <c r="E7" t="str">
+        <v>corr-1</v>
+      </c>
+      <c r="F7" t="str">
+        <v>São Paulo</v>
+      </c>
+      <c r="G7" t="str">
+        <v>SP</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Middle</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Fluxo Normal</v>
+      </c>
+      <c r="J7">
+        <v>10000000</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Aprovado</v>
+      </c>
+      <c r="L7" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="N7" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+      <c r="O7" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>tom-7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Ponte Nova Engenharia Ltda</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Ponte Nova</v>
+      </c>
+      <c r="D8" t="str">
+        <v>07.007.007/0001-07</v>
+      </c>
+      <c r="E8" t="str">
+        <v>corr-1</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Guarulhos</v>
+      </c>
+      <c r="G8" t="str">
+        <v>SP</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Small</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Fluxo Normal</v>
+      </c>
+      <c r="J8">
+        <v>4000000</v>
+      </c>
+      <c r="K8" t="str">
+        <v>Em Análise</v>
+      </c>
+      <c r="L8" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" t="str">
+        <v>2026-04-05</v>
+      </c>
+      <c r="N8" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+      <c r="O8" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>tom-8</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Rodovias Unidas SA</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Rodovias Unidas</v>
+      </c>
+      <c r="D9" t="str">
+        <v>08.008.008/0001-08</v>
+      </c>
+      <c r="E9" t="str">
+        <v>corr-2</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Campinas</v>
+      </c>
+      <c r="G9" t="str">
+        <v>SP</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Corporate</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Prioridade</v>
+      </c>
+      <c r="J9">
+        <v>45000000</v>
+      </c>
+      <c r="K9" t="str">
+        <v>Aprovado</v>
+      </c>
+      <c r="L9" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" t="str">
+        <v>2026-01-20</v>
+      </c>
+      <c r="N9" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+      <c r="O9" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>tom-9</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Saneamento Central Ltda</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Saneamento Central</v>
+      </c>
+      <c r="D10" t="str">
+        <v>09.009.009/0001-09</v>
+      </c>
+      <c r="E10" t="str">
+        <v>corr-2</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Ribeirão Preto</v>
+      </c>
+      <c r="G10" t="str">
+        <v>SP</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Middle</v>
+      </c>
+      <c r="I10" t="str">
+        <v>Fluxo Normal</v>
+      </c>
+      <c r="J10">
+        <v>12000000</v>
+      </c>
+      <c r="K10" t="str">
+        <v>Aprovado</v>
+      </c>
+      <c r="L10" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" t="str">
+        <v>2026-03-12</v>
+      </c>
+      <c r="N10" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+      <c r="O10" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>tom-10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Porto Litoral Logística Ltda</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Porto Litoral</v>
+      </c>
+      <c r="D11" t="str">
+        <v>10.010.010/0001-10</v>
+      </c>
+      <c r="E11" t="str">
+        <v>corr-3</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Santos</v>
+      </c>
+      <c r="G11" t="str">
+        <v>SP</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Large</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Prioridade</v>
+      </c>
+      <c r="J11">
+        <v>30000000</v>
+      </c>
+      <c r="K11" t="str">
+        <v>Aprovado</v>
+      </c>
+      <c r="L11" t="b">
+        <v>1</v>
+      </c>
+      <c r="M11" t="str">
+        <v>2026-03-28</v>
+      </c>
+      <c r="N11" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+      <c r="O11" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>tom-11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Cerrado Construtora Ltda</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Cerrado</v>
+      </c>
+      <c r="D12" t="str">
+        <v>11.011.011/0001-11</v>
+      </c>
+      <c r="E12" t="str">
+        <v>corr-4</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Brasília</v>
+      </c>
+      <c r="G12" t="str">
+        <v>DF</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Middle</v>
+      </c>
+      <c r="I12" t="str">
+        <v>Fluxo Normal</v>
+      </c>
+      <c r="J12">
+        <v>6000000</v>
+      </c>
+      <c r="K12" t="str">
+        <v>Em Análise</v>
+      </c>
+      <c r="L12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M12" t="str">
+        <v>2026-04-18</v>
+      </c>
+      <c r="N12" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+      <c r="O12" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>tom-12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Gaúcha Metal Ltda</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Gaúcha Metal</v>
+      </c>
+      <c r="D13" t="str">
+        <v>12.012.012/0001-12</v>
+      </c>
+      <c r="E13" t="str">
+        <v>corr-5</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Caxias do Sul</v>
+      </c>
+      <c r="G13" t="str">
+        <v>RS</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Small</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Fluxo Normal</v>
+      </c>
+      <c r="J13">
+        <v>3000000</v>
+      </c>
+      <c r="K13" t="str">
+        <v>Aprovado</v>
+      </c>
+      <c r="L13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M13" t="str">
+        <v>2026-02-25</v>
+      </c>
+      <c r="N13" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+      <c r="O13" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O13"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AF6"/>
+  <dimension ref="A1:AF22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2549,9 +2878,1166 @@
         <v>2026-06-01T12:00:00.000Z</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>op-6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>tom-6</v>
+      </c>
+      <c r="C7" t="str">
+        <v>corr-1</v>
+      </c>
+      <c r="D7" t="str">
+        <v>João Pereira</v>
+      </c>
+      <c r="E7" t="str">
+        <v>prod-1</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Garantia de Concorrência</v>
+      </c>
+      <c r="G7" t="str">
+        <v>0432</v>
+      </c>
+      <c r="H7" t="str">
+        <v>SP</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Quente</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Fluxo Normal</v>
+      </c>
+      <c r="K7">
+        <v>8000000</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>2</v>
+      </c>
+      <c r="N7">
+        <v>730</v>
+      </c>
+      <c r="O7" t="str">
+        <v>Emitido</v>
+      </c>
+      <c r="P7" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="Q7">
+        <v>160000</v>
+      </c>
+      <c r="R7" t="str">
+        <v>anos</v>
+      </c>
+      <c r="T7" t="b">
+        <v>1</v>
+      </c>
+      <c r="U7" t="str">
+        <v>2026-02-03</v>
+      </c>
+      <c r="Y7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+      <c r="AF7" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>op-7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>tom-6</v>
+      </c>
+      <c r="C8" t="str">
+        <v>corr-1</v>
+      </c>
+      <c r="D8" t="str">
+        <v>João Pereira</v>
+      </c>
+      <c r="E8" t="str">
+        <v>prod-3</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Garantia de Execução (Performance)</v>
+      </c>
+      <c r="G8" t="str">
+        <v>0435</v>
+      </c>
+      <c r="H8" t="str">
+        <v>SP</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Quente</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Prioridade</v>
+      </c>
+      <c r="K8">
+        <v>15000000</v>
+      </c>
+      <c r="L8">
+        <v>0.9</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>365</v>
+      </c>
+      <c r="O8" t="str">
+        <v>Aprovado</v>
+      </c>
+      <c r="Q8">
+        <v>135000</v>
+      </c>
+      <c r="R8" t="str">
+        <v>anos</v>
+      </c>
+      <c r="T8" t="b">
+        <v>1</v>
+      </c>
+      <c r="U8" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="Y8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+      <c r="AF8" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>op-8</v>
+      </c>
+      <c r="B9" t="str">
+        <v>tom-7</v>
+      </c>
+      <c r="C9" t="str">
+        <v>corr-1</v>
+      </c>
+      <c r="D9" t="str">
+        <v>João Pereira</v>
+      </c>
+      <c r="E9" t="str">
+        <v>prod-2</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Garantia Judicial Cível</v>
+      </c>
+      <c r="G9" t="str">
+        <v>0775</v>
+      </c>
+      <c r="H9" t="str">
+        <v>SP</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Morno</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Fluxo Normal</v>
+      </c>
+      <c r="K9">
+        <v>3000000</v>
+      </c>
+      <c r="L9">
+        <v>1.1</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>365</v>
+      </c>
+      <c r="O9" t="str">
+        <v>Em Análise</v>
+      </c>
+      <c r="Q9">
+        <v>33000</v>
+      </c>
+      <c r="R9" t="str">
+        <v>anos</v>
+      </c>
+      <c r="T9" t="b">
+        <v>1</v>
+      </c>
+      <c r="U9" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="Y9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+      <c r="AF9" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>op-9</v>
+      </c>
+      <c r="B10" t="str">
+        <v>tom-1</v>
+      </c>
+      <c r="C10" t="str">
+        <v>corr-1</v>
+      </c>
+      <c r="D10" t="str">
+        <v>João Pereira</v>
+      </c>
+      <c r="E10" t="str">
+        <v>prod-1</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Garantia de Concorrência</v>
+      </c>
+      <c r="G10" t="str">
+        <v>0432</v>
+      </c>
+      <c r="H10" t="str">
+        <v>SP</v>
+      </c>
+      <c r="I10" t="str">
+        <v>Quente</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Fluxo Normal</v>
+      </c>
+      <c r="K10">
+        <v>12000000</v>
+      </c>
+      <c r="L10">
+        <v>0.85</v>
+      </c>
+      <c r="M10">
+        <v>2</v>
+      </c>
+      <c r="N10">
+        <v>730</v>
+      </c>
+      <c r="O10" t="str">
+        <v>Emitido</v>
+      </c>
+      <c r="P10" t="str">
+        <v>2026-01-25</v>
+      </c>
+      <c r="Q10">
+        <v>204000</v>
+      </c>
+      <c r="R10" t="str">
+        <v>anos</v>
+      </c>
+      <c r="T10" t="b">
+        <v>1</v>
+      </c>
+      <c r="U10" t="str">
+        <v>2026-01-10</v>
+      </c>
+      <c r="Y10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+      <c r="AF10" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>op-10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>tom-8</v>
+      </c>
+      <c r="C11" t="str">
+        <v>corr-2</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Maria Souza</v>
+      </c>
+      <c r="E11" t="str">
+        <v>prod-3</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Garantia de Execução (Performance)</v>
+      </c>
+      <c r="G11" t="str">
+        <v>0435</v>
+      </c>
+      <c r="H11" t="str">
+        <v>SP</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Quente</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Prioridade</v>
+      </c>
+      <c r="K11">
+        <v>40000000</v>
+      </c>
+      <c r="L11">
+        <v>0.7</v>
+      </c>
+      <c r="M11">
+        <v>3</v>
+      </c>
+      <c r="N11">
+        <v>1095</v>
+      </c>
+      <c r="O11" t="str">
+        <v>Emitido</v>
+      </c>
+      <c r="P11" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="Q11">
+        <v>840000</v>
+      </c>
+      <c r="R11" t="str">
+        <v>anos</v>
+      </c>
+      <c r="T11" t="b">
+        <v>1</v>
+      </c>
+      <c r="U11" t="str">
+        <v>2026-03-02</v>
+      </c>
+      <c r="Y11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+      <c r="AF11" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>op-11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>tom-8</v>
+      </c>
+      <c r="C12" t="str">
+        <v>corr-2</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Maria Souza</v>
+      </c>
+      <c r="E12" t="str">
+        <v>prod-1</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Garantia de Concorrência</v>
+      </c>
+      <c r="G12" t="str">
+        <v>0432</v>
+      </c>
+      <c r="H12" t="str">
+        <v>SP</v>
+      </c>
+      <c r="I12" t="str">
+        <v>Morno</v>
+      </c>
+      <c r="J12" t="str">
+        <v>Fluxo Normal</v>
+      </c>
+      <c r="K12">
+        <v>25000000</v>
+      </c>
+      <c r="L12">
+        <v>0.8</v>
+      </c>
+      <c r="M12">
+        <v>2</v>
+      </c>
+      <c r="N12">
+        <v>730</v>
+      </c>
+      <c r="O12" t="str">
+        <v>Aprovado</v>
+      </c>
+      <c r="Q12">
+        <v>400000</v>
+      </c>
+      <c r="R12" t="str">
+        <v>anos</v>
+      </c>
+      <c r="T12" t="b">
+        <v>1</v>
+      </c>
+      <c r="U12" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="Y12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+      <c r="AF12" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>op-12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>tom-9</v>
+      </c>
+      <c r="C13" t="str">
+        <v>corr-2</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Maria Souza</v>
+      </c>
+      <c r="E13" t="str">
+        <v>prod-5</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Garantia Aduaneira</v>
+      </c>
+      <c r="G13" t="str">
+        <v>0990</v>
+      </c>
+      <c r="H13" t="str">
+        <v>SP</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Morno</v>
+      </c>
+      <c r="J13" t="str">
+        <v>Fluxo Normal</v>
+      </c>
+      <c r="K13">
+        <v>6000000</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>365</v>
+      </c>
+      <c r="O13" t="str">
+        <v>Emitido</v>
+      </c>
+      <c r="P13" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="Q13">
+        <v>60000</v>
+      </c>
+      <c r="R13" t="str">
+        <v>anos</v>
+      </c>
+      <c r="T13" t="b">
+        <v>1</v>
+      </c>
+      <c r="U13" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="Y13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+      <c r="AF13" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>op-13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>tom-2</v>
+      </c>
+      <c r="C14" t="str">
+        <v>corr-2</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Maria Souza</v>
+      </c>
+      <c r="E14" t="str">
+        <v>prod-3</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Garantia de Execução (Performance)</v>
+      </c>
+      <c r="G14" t="str">
+        <v>0435</v>
+      </c>
+      <c r="H14" t="str">
+        <v>SP</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Quente</v>
+      </c>
+      <c r="J14" t="str">
+        <v>Prioridade</v>
+      </c>
+      <c r="K14">
+        <v>18000000</v>
+      </c>
+      <c r="L14">
+        <v>0.95</v>
+      </c>
+      <c r="M14">
+        <v>2</v>
+      </c>
+      <c r="N14">
+        <v>730</v>
+      </c>
+      <c r="O14" t="str">
+        <v>Em Análise</v>
+      </c>
+      <c r="Q14">
+        <v>342000</v>
+      </c>
+      <c r="R14" t="str">
+        <v>anos</v>
+      </c>
+      <c r="T14" t="b">
+        <v>1</v>
+      </c>
+      <c r="U14" t="str">
+        <v>2026-06-20</v>
+      </c>
+      <c r="Y14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+      <c r="AF14" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>op-14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>tom-10</v>
+      </c>
+      <c r="C15" t="str">
+        <v>corr-3</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Carlos Lima</v>
+      </c>
+      <c r="E15" t="str">
+        <v>prod-3</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Garantia de Execução (Performance)</v>
+      </c>
+      <c r="G15" t="str">
+        <v>0435</v>
+      </c>
+      <c r="H15" t="str">
+        <v>SP</v>
+      </c>
+      <c r="I15" t="str">
+        <v>Quente</v>
+      </c>
+      <c r="J15" t="str">
+        <v>Prioridade</v>
+      </c>
+      <c r="K15">
+        <v>22000000</v>
+      </c>
+      <c r="L15">
+        <v>0.75</v>
+      </c>
+      <c r="M15">
+        <v>2</v>
+      </c>
+      <c r="N15">
+        <v>730</v>
+      </c>
+      <c r="O15" t="str">
+        <v>Emitido</v>
+      </c>
+      <c r="P15" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="Q15">
+        <v>330000</v>
+      </c>
+      <c r="R15" t="str">
+        <v>anos</v>
+      </c>
+      <c r="T15" t="b">
+        <v>1</v>
+      </c>
+      <c r="U15" t="str">
+        <v>2026-04-04</v>
+      </c>
+      <c r="Y15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+      <c r="AF15" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>op-15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>tom-10</v>
+      </c>
+      <c r="C16" t="str">
+        <v>corr-3</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Carlos Lima</v>
+      </c>
+      <c r="E16" t="str">
+        <v>prod-1</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Garantia de Concorrência</v>
+      </c>
+      <c r="G16" t="str">
+        <v>0432</v>
+      </c>
+      <c r="H16" t="str">
+        <v>SP</v>
+      </c>
+      <c r="I16" t="str">
+        <v>Morno</v>
+      </c>
+      <c r="J16" t="str">
+        <v>Fluxo Normal</v>
+      </c>
+      <c r="K16">
+        <v>9000000</v>
+      </c>
+      <c r="L16">
+        <v>0.9</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>365</v>
+      </c>
+      <c r="O16" t="str">
+        <v>Aprovado</v>
+      </c>
+      <c r="Q16">
+        <v>81000</v>
+      </c>
+      <c r="R16" t="str">
+        <v>anos</v>
+      </c>
+      <c r="T16" t="b">
+        <v>1</v>
+      </c>
+      <c r="U16" t="str">
+        <v>2026-05-14</v>
+      </c>
+      <c r="Y16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+      <c r="AF16" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>op-16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>tom-3</v>
+      </c>
+      <c r="C17" t="str">
+        <v>corr-3</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Carlos Lima</v>
+      </c>
+      <c r="E17" t="str">
+        <v>prod-2</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Garantia Judicial Cível</v>
+      </c>
+      <c r="G17" t="str">
+        <v>0775</v>
+      </c>
+      <c r="H17" t="str">
+        <v>SP</v>
+      </c>
+      <c r="I17" t="str">
+        <v>Quente</v>
+      </c>
+      <c r="J17" t="str">
+        <v>Urgente</v>
+      </c>
+      <c r="K17">
+        <v>14000000</v>
+      </c>
+      <c r="L17">
+        <v>0.6</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>365</v>
+      </c>
+      <c r="O17" t="str">
+        <v>Comitê</v>
+      </c>
+      <c r="Q17">
+        <v>84000</v>
+      </c>
+      <c r="R17" t="str">
+        <v>anos</v>
+      </c>
+      <c r="T17" t="b">
+        <v>1</v>
+      </c>
+      <c r="U17" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="Y17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+      <c r="AF17" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>op-17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>tom-11</v>
+      </c>
+      <c r="C18" t="str">
+        <v>corr-4</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Ana Castro</v>
+      </c>
+      <c r="E18" t="str">
+        <v>prod-4</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Fiança Locatícia Residencial</v>
+      </c>
+      <c r="G18" t="str">
+        <v>0870</v>
+      </c>
+      <c r="H18" t="str">
+        <v>DF</v>
+      </c>
+      <c r="I18" t="str">
+        <v>Frio</v>
+      </c>
+      <c r="J18" t="str">
+        <v>Fluxo Normal</v>
+      </c>
+      <c r="K18">
+        <v>4000000</v>
+      </c>
+      <c r="L18">
+        <v>1.3</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
+        <v>365</v>
+      </c>
+      <c r="O18" t="str">
+        <v>Emitido</v>
+      </c>
+      <c r="P18" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="Q18">
+        <v>52000</v>
+      </c>
+      <c r="R18" t="str">
+        <v>anos</v>
+      </c>
+      <c r="T18" t="b">
+        <v>1</v>
+      </c>
+      <c r="U18" t="str">
+        <v>2026-02-08</v>
+      </c>
+      <c r="Y18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+      <c r="AF18" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>op-18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>tom-11</v>
+      </c>
+      <c r="C19" t="str">
+        <v>corr-4</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Ana Castro</v>
+      </c>
+      <c r="E19" t="str">
+        <v>prod-1</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Garantia de Concorrência</v>
+      </c>
+      <c r="G19" t="str">
+        <v>0432</v>
+      </c>
+      <c r="H19" t="str">
+        <v>DF</v>
+      </c>
+      <c r="I19" t="str">
+        <v>Frio</v>
+      </c>
+      <c r="J19" t="str">
+        <v>Fluxo Normal</v>
+      </c>
+      <c r="K19">
+        <v>2500000</v>
+      </c>
+      <c r="L19">
+        <v>1.5</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
+      </c>
+      <c r="N19">
+        <v>365</v>
+      </c>
+      <c r="O19" t="str">
+        <v>Para Analisar</v>
+      </c>
+      <c r="Q19">
+        <v>37500</v>
+      </c>
+      <c r="R19" t="str">
+        <v>anos</v>
+      </c>
+      <c r="T19" t="b">
+        <v>1</v>
+      </c>
+      <c r="U19" t="str">
+        <v>2026-07-05</v>
+      </c>
+      <c r="Y19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+      <c r="AF19" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>op-19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>tom-4</v>
+      </c>
+      <c r="C20" t="str">
+        <v>corr-4</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Ana Castro</v>
+      </c>
+      <c r="E20" t="str">
+        <v>prod-4</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Fiança Locatícia Residencial</v>
+      </c>
+      <c r="G20" t="str">
+        <v>0870</v>
+      </c>
+      <c r="H20" t="str">
+        <v>DF</v>
+      </c>
+      <c r="I20" t="str">
+        <v>Frio</v>
+      </c>
+      <c r="J20" t="str">
+        <v>Fluxo Normal</v>
+      </c>
+      <c r="K20">
+        <v>1500000</v>
+      </c>
+      <c r="L20">
+        <v>1.8</v>
+      </c>
+      <c r="M20">
+        <v>1</v>
+      </c>
+      <c r="N20">
+        <v>365</v>
+      </c>
+      <c r="O20" t="str">
+        <v>Aprovado</v>
+      </c>
+      <c r="Q20">
+        <v>27000</v>
+      </c>
+      <c r="R20" t="str">
+        <v>anos</v>
+      </c>
+      <c r="T20" t="b">
+        <v>1</v>
+      </c>
+      <c r="U20" t="str">
+        <v>2026-06-11</v>
+      </c>
+      <c r="Y20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+      <c r="AF20" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>op-20</v>
+      </c>
+      <c r="B21" t="str">
+        <v>tom-12</v>
+      </c>
+      <c r="C21" t="str">
+        <v>corr-5</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Pedro Rocha</v>
+      </c>
+      <c r="E21" t="str">
+        <v>prod-1</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Garantia de Concorrência</v>
+      </c>
+      <c r="G21" t="str">
+        <v>0432</v>
+      </c>
+      <c r="H21" t="str">
+        <v>RS</v>
+      </c>
+      <c r="I21" t="str">
+        <v>Morno</v>
+      </c>
+      <c r="J21" t="str">
+        <v>Fluxo Normal</v>
+      </c>
+      <c r="K21">
+        <v>3500000</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+      <c r="M21">
+        <v>1</v>
+      </c>
+      <c r="N21">
+        <v>365</v>
+      </c>
+      <c r="O21" t="str">
+        <v>Emitido</v>
+      </c>
+      <c r="P21" t="str">
+        <v>2026-03-26</v>
+      </c>
+      <c r="Q21">
+        <v>35000</v>
+      </c>
+      <c r="R21" t="str">
+        <v>anos</v>
+      </c>
+      <c r="T21" t="b">
+        <v>1</v>
+      </c>
+      <c r="U21" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="Y21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+      <c r="AF21" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>op-21</v>
+      </c>
+      <c r="B22" t="str">
+        <v>tom-5</v>
+      </c>
+      <c r="C22" t="str">
+        <v>corr-5</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Pedro Rocha</v>
+      </c>
+      <c r="E22" t="str">
+        <v>prod-3</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Garantia de Execução (Performance)</v>
+      </c>
+      <c r="G22" t="str">
+        <v>0435</v>
+      </c>
+      <c r="H22" t="str">
+        <v>RS</v>
+      </c>
+      <c r="I22" t="str">
+        <v>Morno</v>
+      </c>
+      <c r="J22" t="str">
+        <v>Fluxo Normal</v>
+      </c>
+      <c r="K22">
+        <v>2000000</v>
+      </c>
+      <c r="L22">
+        <v>1.1</v>
+      </c>
+      <c r="M22">
+        <v>2</v>
+      </c>
+      <c r="N22">
+        <v>730</v>
+      </c>
+      <c r="O22" t="str">
+        <v>Em Análise</v>
+      </c>
+      <c r="Q22">
+        <v>44000</v>
+      </c>
+      <c r="R22" t="str">
+        <v>anos</v>
+      </c>
+      <c r="T22" t="b">
+        <v>1</v>
+      </c>
+      <c r="U22" t="str">
+        <v>2026-05-19</v>
+      </c>
+      <c r="Y22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+      <c r="AF22" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AF6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AF22"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/public/sandbox-dados.xlsx
+++ b/public/sandbox-dados.xlsx
@@ -4869,4 +4869,237 @@
     <ignoredError numberStoredAsText="1" sqref="A1:M6"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010049A15EF64A6E6D45BC3F8B85F291981F" ma:contentTypeVersion="12" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="1080b8e62f11c78000bf934e727016da">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="da3e1692-5e12-4fdc-8f71-b45bb92bf479" xmlns:ns3="65478c58-49f4-4622-a823-6bde131dcefd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f09fde6e82e708a3c3b08a16c1e7fa2b" ns2:_="" ns3:_="">
+    <xsd:import namespace="da3e1692-5e12-4fdc-8f71-b45bb92bf479"/>
+    <xsd:import namespace="65478c58-49f4-4622-a823-6bde131dcefd"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="da3e1692-5e12-4fdc-8f71-b45bb92bf479" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="15" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="17" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Marcações de imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="662fd93e-9c87-4599-9d0e-ce60c311312f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="19" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="65478c58-49f4-4622-a823-6bde131dcefd" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="18" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{dae16d1f-a00d-451c-996f-52f648594a2a}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="65478c58-49f4-4622-a823-6bde131dcefd">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="da3e1692-5e12-4fdc-8f71-b45bb92bf479">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="65478c58-49f4-4622-a823-6bde131dcefd" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA7A6150-E1FA-4795-8046-801E221D72AD}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A616CE8-6698-42A3-9824-D8BDB273316A}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91998800-E8FF-44E1-8471-19FED979101B}"/>
 </file>